--- a/data/gravel/Kona Rove 2025.xlsx
+++ b/data/gravel/Kona Rove 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18BDCF50-036C-064C-9CE6-82BC6BB7AC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04634BA-305A-E748-9A3B-2FCF662AF5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32680" yWindow="-22200" windowWidth="24640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -269,9 +269,6 @@
     <t>front_center</t>
   </si>
   <si>
-    <t>suspension</t>
-  </si>
-  <si>
     <t>usd</t>
   </si>
   <si>
@@ -333,6 +330,9 @@
   </si>
   <si>
     <t>external</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -706,7 +706,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -730,7 +730,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -738,7 +738,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -746,7 +746,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="3">
         <v>48</v>
@@ -772,7 +772,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3">
         <v>480</v>
@@ -798,7 +798,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="3">
         <v>515</v>
@@ -824,7 +824,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="3">
         <v>372</v>
@@ -850,7 +850,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" s="3">
         <v>532</v>
@@ -876,7 +876,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" s="3">
         <v>735</v>
@@ -928,7 +928,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="3">
         <v>90</v>
@@ -954,7 +954,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="3">
         <v>75</v>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C17" s="3">
         <v>435</v>
@@ -1006,7 +1006,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C18" s="3">
         <v>74</v>
@@ -1032,7 +1032,7 @@
         <v>76</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" s="3">
         <v>268</v>
@@ -1058,7 +1058,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" s="3">
         <v>1016</v>
@@ -1084,7 +1084,7 @@
         <v>77</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C21" s="3">
         <v>592</v>
@@ -1110,7 +1110,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C22" s="3">
         <v>400</v>
@@ -1136,7 +1136,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C23" s="3">
         <v>50</v>
@@ -1409,7 +1409,7 @@
         <v>70</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -1417,7 +1417,7 @@
         <v>31</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -1542,7 +1542,7 @@
         <v>51</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -1641,7 +1641,7 @@
         <v>65</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Kona Rove 2025.xlsx
+++ b/data/gravel/Kona Rove 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04634BA-305A-E748-9A3B-2FCF662AF5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBAF0B2-4BBA-BB4E-A2AD-4CFCBC5CDC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32680" yWindow="-22200" windowWidth="24640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="101">
   <si>
     <t>brand</t>
   </si>
@@ -326,13 +326,16 @@
     <t>FORK OFFSET </t>
   </si>
   <si>
-    <t>Rove LTD</t>
-  </si>
-  <si>
     <t>external</t>
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://konaworld.com/cdn/shop/files/my23_rove_ltd.jpg?v=1733096947&amp;width=2000</t>
+  </si>
+  <si>
+    <t>Rove</t>
   </si>
 </sst>
 </file>
@@ -706,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -731,6 +734,11 @@
       </c>
       <c r="B5" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1409,7 +1417,7 @@
         <v>70</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -1542,7 +1550,7 @@
         <v>51</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Kona Rove 2025.xlsx
+++ b/data/gravel/Kona Rove 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBAF0B2-4BBA-BB4E-A2AD-4CFCBC5CDC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5A6C13-88B3-E246-BC1B-73711D20F20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -269,9 +269,6 @@
     <t>front_center</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>a8:h34</t>
   </si>
   <si>
@@ -336,6 +333,15 @@
   </si>
   <si>
     <t>Rove</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Ferndale, Washington, USA</t>
   </si>
 </sst>
 </file>
@@ -690,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -709,7 +715,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -733,12 +739,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -746,7 +752,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -754,7 +760,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="3">
         <v>48</v>
@@ -780,7 +786,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3">
         <v>480</v>
@@ -806,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="3">
         <v>515</v>
@@ -832,7 +838,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" s="3">
         <v>372</v>
@@ -858,7 +864,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C12" s="3">
         <v>532</v>
@@ -884,7 +890,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C13" s="3">
         <v>735</v>
@@ -936,7 +942,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C15" s="3">
         <v>90</v>
@@ -962,7 +968,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" s="3">
         <v>75</v>
@@ -988,7 +994,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C17" s="3">
         <v>435</v>
@@ -1014,7 +1020,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C18" s="3">
         <v>74</v>
@@ -1040,7 +1046,7 @@
         <v>76</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C19" s="3">
         <v>268</v>
@@ -1066,7 +1072,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C20" s="3">
         <v>1016</v>
@@ -1092,7 +1098,7 @@
         <v>77</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" s="3">
         <v>592</v>
@@ -1118,7 +1124,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C22" s="3">
         <v>400</v>
@@ -1144,7 +1150,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C23" s="3">
         <v>50</v>
@@ -1417,7 +1423,7 @@
         <v>70</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -1425,7 +1431,7 @@
         <v>31</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -1550,7 +1556,7 @@
         <v>51</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -1649,7 +1655,15 @@
         <v>65</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>78</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>101</v>
+      </c>
+      <c r="B75" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Kona Rove 2025.xlsx
+++ b/data/gravel/Kona Rove 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5A6C13-88B3-E246-BC1B-73711D20F20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF60EC2-9ADD-054B-824C-C74E62FC3A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -342,6 +342,24 @@
   </si>
   <si>
     <t>Ferndale, Washington, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -696,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1500,169 +1518,199 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="1"/>
+        <v>103</v>
+      </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="1"/>
+        <v>104</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53">
-        <v>27.2</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>48</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B57" s="1"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>49</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B58" s="1"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B59">
+        <v>27.2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>53</v>
-      </c>
-      <c r="B62" s="1"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>56</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>58</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>71</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>59</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>71</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B68" s="1"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>60</v>
-      </c>
-      <c r="B69" s="1"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>61</v>
-      </c>
-      <c r="B70" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>62</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1950</v>
+        <v>56</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>63</v>
-      </c>
-      <c r="B72">
-        <v>3599</v>
+        <v>57</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>64</v>
-      </c>
-      <c r="B73" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>60</v>
+      </c>
+      <c r="B75" s="1"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>61</v>
+      </c>
+      <c r="B76" s="1"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="1"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>101</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>102</v>
       </c>
     </row>
